--- a/InputData/trans/BRAaCTSC/BAU Rng Anxiety and Charge Time Shadow Costs.xlsx
+++ b/InputData/trans/BRAaCTSC/BAU Rng Anxiety and Charge Time Shadow Costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10402"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BRAaCTSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/BRAaCTSC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC02F20B-346B-4E17-A776-81D370EAD24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C29671-74B0-0F4D-B1D6-B3C4FE966A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -342,7 +342,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1595,235 +1594,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="8">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B5" s="7">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B10" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="8">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B12" s="7">
         <v>2013</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B15" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="8">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="7">
         <v>2018</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="8">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="7">
         <v>2021</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B27" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="8">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B29" s="7">
         <v>2016</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="7" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B34" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="8">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B36" s="7">
         <v>2021</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="9" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B38" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -1842,18 +1841,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{341A17B3-AFD9-42DA-AB68-E46FC6CF1D40}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.5" customWidth="1"/>
+    <col min="2" max="2" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1861,12 +1860,12 @@
         <v>-0.36099999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1874,7 +1873,7 @@
         <v>1.268</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1882,7 +1881,7 @@
         <v>-0.11600000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>2020</v>
       </c>
@@ -1893,7 +1892,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1908,106 +1907,106 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9">
         <v>2.59</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>3</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>4.12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10">
         <v>68.703000000000003</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f>income</f>
         <v>68.703000000000003</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f>B10</f>
         <v>68.703000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <f>($B$4/$B$2*B9*(1-B8/B9)+$B$5/$B$2*B9^2*(1-B8^2/B9^2))*LN(income)*About!$B$53</f>
         <v>7.8828464065137096</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <f>($B$4/$B$2*C9*(1-C8/C9)+$B$5/$B$2*C9^2*(1-C8^2/C9^2))*LN(income)*About!$B$53</f>
         <v>5.2099509525186276</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <f>($B$4/$B$2*D9*(1-D8/D9)+$B$5/$B$2*D9^2*(1-D8^2/D9^2))*LN(income)*About!$B$53</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="B17">
         <v>7500</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="5">
         <v>0.05</v>
       </c>
       <c r="B18">
         <v>1750</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="5">
         <v>0.1</v>
       </c>
       <c r="B19">
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="5">
         <v>1</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -2015,7 +2014,7 @@
         <v>120045</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -2023,7 +2022,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>2020</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -2057,7 +2056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -2077,29 +2076,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2020</v>
       </c>
@@ -2108,7 +2107,7 @@
         <v>8780.9012221455905</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2027</v>
       </c>
@@ -2117,7 +2116,7 @@
         <v>6349.8416004663277</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>2030</v>
       </c>
@@ -2126,7 +2125,7 @@
         <v>5437.3452824734923</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>2050</v>
       </c>
@@ -2145,23 +2144,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D98A39-3A78-451F-9516-0CF8624C92E2}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -2169,8 +2168,8 @@
         <v>7500000000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B5">
@@ -2178,16 +2177,16 @@
         <v>9375000000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>64</v>
       </c>
       <c r="B7">
         <v>24443</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B9" s="3">
@@ -2205,13 +2204,13 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AZ2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -2308,8 +2307,68 @@
       <c r="AF1" s="4">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2437,7 +2496,86 @@
         <f t="array" ref="AF2">TREND(Calculations!$B$38:$B$39,Calculations!$A$38:$A$39,BRAaCTSC!AF1)</f>
         <v>0</v>
       </c>
-      <c r="AG2" s="3"/>
+      <c r="AG2" s="3">
+        <f>AF2</f>
+        <v>0</v>
+      </c>
+      <c r="AH2" s="3">
+        <f t="shared" ref="AH2:AZ2" si="0">AG2</f>
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
